--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amazon" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FlipKart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Amazon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FlipKart" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D3" s="42" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G3" s="42" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="I3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J3" s="42" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M3" s="42" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="O3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P3" s="42" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Q3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="M5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q5" s="42" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="42" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="L8" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M8" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N8" s="42" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" s="42" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K10" s="42" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N10" s="42" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P10" s="42" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Q10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="M12" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N12" s="42" t="inlineStr">
@@ -1939,17 +1939,17 @@
       </c>
       <c r="M13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P13" s="42" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="Q15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="I16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K16" s="42" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G17" s="42" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="N17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O17" s="42" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="M18" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N18" s="42" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="O18" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P18" s="42" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D19" s="42" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J19" s="42" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Q20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K9" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" s="42" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="G10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I10" s="42" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" s="42" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H19" s="42" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="G20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H20" s="42" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L20" s="42" t="inlineStr">

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1193,77 +1193,77 @@
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G3" s="42" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" s="42" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="F16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G16" s="42" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1019,17 +1019,17 @@
       </c>
       <c r="C3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F3" s="42" t="inlineStr">
@@ -1039,57 +1039,57 @@
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
@@ -1280,77 +1280,77 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G15" s="42" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="F16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G16" s="42" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1059,37 +1059,37 @@
       </c>
       <c r="K3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1146,37 +1146,37 @@
       </c>
       <c r="K4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
@@ -1233,37 +1233,37 @@
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1280,77 +1280,77 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="K7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O7" s="42" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="P7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q7" s="42" t="inlineStr">
@@ -1494,22 +1494,22 @@
       </c>
       <c r="K8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O8" s="42" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="P8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q8" s="42" t="inlineStr">
@@ -1581,22 +1581,22 @@
       </c>
       <c r="K9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O9" s="42" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="P9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q9" s="42" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
@@ -1668,22 +1668,22 @@
       </c>
       <c r="K10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O10" s="42" t="inlineStr">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="K11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O11" s="42" t="inlineStr">
@@ -1842,17 +1842,17 @@
       </c>
       <c r="K12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N12" s="42" t="inlineStr">
@@ -1929,17 +1929,17 @@
       </c>
       <c r="K13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N13" s="42" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" s="42" t="inlineStr">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="K15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N15" s="42" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="F16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G16" s="42" t="inlineStr">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="K16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N16" s="42" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G17" s="42" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N17" s="42" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="L18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N18" s="42" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="L19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N19" s="42" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N20" s="42" t="inlineStr">

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1019,42 +1019,42 @@
       </c>
       <c r="C3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K3" s="42" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="N3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O3" s="42" t="inlineStr">
@@ -1106,32 +1106,32 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="J4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K4" s="42" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M4" s="42" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="N4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="O4" s="42" t="inlineStr">
@@ -1193,32 +1193,32 @@
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="N5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="O5" s="42" t="inlineStr">
@@ -1280,42 +1280,42 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K6" s="42" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="N6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="O6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P6" s="42" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1372,27 +1372,27 @@
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="J7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K7" s="42" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="L7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M7" s="42" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="N7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O7" s="42" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Q7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1459,27 +1459,27 @@
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I8" s="42" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="J8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K8" s="42" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M8" s="42" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="N8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O8" s="42" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Q8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1546,17 +1546,17 @@
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G9" s="42" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I9" s="42" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K9" s="42" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="L9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M9" s="42" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="N9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O9" s="42" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Q9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1628,22 +1628,22 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I10" s="42" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M10" s="42" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O10" s="42" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="P10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1720,17 +1720,17 @@
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G11" s="42" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I11" s="42" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="L11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M11" s="42" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="N11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O11" s="42" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="P11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1807,17 +1807,17 @@
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G12" s="42" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I12" s="42" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="L12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M12" s="42" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="P12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1894,17 +1894,17 @@
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G13" s="42" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="H13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I13" s="42" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="L13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M13" s="42" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="P13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -2000,17 +2000,17 @@
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G15" s="42" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="H15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I15" s="42" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M15" s="42" t="inlineStr">
@@ -2060,12 +2060,12 @@
       </c>
       <c r="P15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G16" s="42" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I16" s="42" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="L16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M16" s="42" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="P16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
       </c>
       <c r="D17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G17" s="42" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="H17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I17" s="42" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="K17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M17" s="42" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="P17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -2256,22 +2256,22 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G18" s="42" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="H18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I18" s="42" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="K18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M18" s="42" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="P18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G19" s="42" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I19" s="42" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="K19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M19" s="42" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="P19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -2435,17 +2435,17 @@
       </c>
       <c r="D20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I20" s="42" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L20" s="42" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="P20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1019,62 +1019,62 @@
       </c>
       <c r="C3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="J3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O3" s="42" t="inlineStr">
@@ -1106,32 +1106,32 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="E4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="J4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="K4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L4" s="42" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="M4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N4" s="42" t="inlineStr">
@@ -1193,47 +1193,47 @@
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="M5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O5" s="42" t="inlineStr">
@@ -1280,47 +1280,47 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
@@ -1372,62 +1372,62 @@
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M7" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O7" s="42" t="inlineStr">
+        <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="E7" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="F7" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="G7" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="H7" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="I7" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="K7" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="L7" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M7" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="N7" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O7" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="42" t="inlineStr">
@@ -1459,62 +1459,62 @@
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M8" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O8" s="42" t="inlineStr">
+        <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="E8" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="F8" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="G8" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="H8" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="I8" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="K8" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="L8" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M8" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="N8" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O8" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="P8" s="42" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G9" s="42" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I9" s="42" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="J9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" s="42" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="M9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N9" s="42" t="inlineStr">
@@ -1628,37 +1628,37 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J10" s="42" t="inlineStr">
@@ -1668,17 +1668,17 @@
       </c>
       <c r="K10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N10" s="42" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q10" s="42" t="inlineStr">
@@ -1720,17 +1720,17 @@
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" s="42" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I11" s="42" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="K11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N11" s="42" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="P11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q11" s="42" t="inlineStr">
@@ -1807,17 +1807,17 @@
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G12" s="42" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" s="42" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="K12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L12" s="42" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="M12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N12" s="42" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="P12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q12" s="42" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G13" s="42" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="H13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I13" s="42" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="K13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L13" s="42" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="M13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O13" s="42" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="P13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q13" s="42" t="inlineStr">
@@ -2000,27 +2000,27 @@
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I15" s="42" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="J15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L15" s="42" t="inlineStr">
@@ -2045,22 +2045,22 @@
       </c>
       <c r="M15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q15" s="42" t="inlineStr">
@@ -2082,47 +2082,47 @@
       </c>
       <c r="C16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L16" s="42" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="M16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q16" s="42" t="inlineStr">
@@ -2169,32 +2169,32 @@
       </c>
       <c r="C17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I17" s="42" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="J17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" s="42" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="M17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N17" s="42" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="P17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2256,22 +2256,22 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G18" s="42" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="H18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I18" s="42" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="K18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L18" s="42" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="M18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N18" s="42" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="P18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2348,27 +2348,27 @@
       </c>
       <c r="D19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="E19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="G19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" s="42" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="J19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L19" s="42" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="M19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O19" s="42" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="P19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2435,17 +2435,17 @@
       </c>
       <c r="D20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="E20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I20" s="42" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L20" s="42" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N20" s="42" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="P20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1019,27 +1019,27 @@
       </c>
       <c r="C3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
@@ -1049,22 +1049,22 @@
       </c>
       <c r="I3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M3" s="42" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="N3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O3" s="42" t="inlineStr">
@@ -1106,27 +1106,27 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H4" s="42" t="inlineStr">
@@ -1136,22 +1136,22 @@
       </c>
       <c r="I4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M4" s="42" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="N4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O4" s="42" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
@@ -1223,22 +1223,22 @@
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="N5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O5" s="42" t="inlineStr">
@@ -1280,22 +1280,22 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
@@ -1310,22 +1310,22 @@
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="N6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O6" s="42" t="inlineStr">
@@ -1367,22 +1367,22 @@
       </c>
       <c r="C7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G7" s="42" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="J7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K7" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M7" s="42" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="N7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O7" s="42" t="inlineStr">
@@ -1454,22 +1454,22 @@
       </c>
       <c r="C8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G8" s="42" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="J8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K8" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L8" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M8" s="42" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="N8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O8" s="42" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G9" s="42" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="J9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K9" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" s="42" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="N9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P9" s="42" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J10" s="42" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="K10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M10" s="42" t="inlineStr">
@@ -1683,17 +1683,17 @@
       </c>
       <c r="N10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q10" s="42" t="inlineStr">
@@ -1715,22 +1715,22 @@
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G11" s="42" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="L11" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M11" s="42" t="inlineStr">
@@ -1770,17 +1770,17 @@
       </c>
       <c r="N11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q11" s="42" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="C12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G12" s="42" t="inlineStr">
@@ -1857,17 +1857,17 @@
       </c>
       <c r="N12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q12" s="42" t="inlineStr">
@@ -1889,22 +1889,22 @@
       </c>
       <c r="C13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G13" s="42" t="inlineStr">
@@ -1944,17 +1944,17 @@
       </c>
       <c r="N13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q13" s="42" t="inlineStr">
@@ -1995,22 +1995,22 @@
       </c>
       <c r="C15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G15" s="42" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="I15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" s="42" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="K15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M15" s="42" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="N15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q15" s="42" t="inlineStr">
@@ -2082,22 +2082,22 @@
       </c>
       <c r="C16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G16" s="42" t="inlineStr">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="K16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M16" s="42" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="N16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q16" s="42" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="C17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E17" s="42" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G17" s="42" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="J17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K17" s="42" t="inlineStr">
@@ -2224,22 +2224,22 @@
       </c>
       <c r="N17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="F18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G18" s="42" t="inlineStr">
@@ -2311,22 +2311,22 @@
       </c>
       <c r="N18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D19" s="42" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G19" s="42" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K19" s="42" t="inlineStr">
@@ -2398,22 +2398,22 @@
       </c>
       <c r="N19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D20" s="42" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L20" s="42" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="P20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1019,52 +1019,52 @@
       </c>
       <c r="C3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M3" s="42" t="inlineStr">
@@ -1074,22 +1074,22 @@
       </c>
       <c r="N3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="O3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="E4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" s="42" t="inlineStr">
@@ -1136,22 +1136,22 @@
       </c>
       <c r="I4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="J4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="K4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M4" s="42" t="inlineStr">
@@ -1161,22 +1161,22 @@
       </c>
       <c r="N4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="O4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1193,22 +1193,22 @@
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
@@ -1223,22 +1223,22 @@
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
@@ -1248,22 +1248,22 @@
       </c>
       <c r="N5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1280,22 +1280,22 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
@@ -1305,27 +1305,27 @@
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
@@ -1335,22 +1335,22 @@
       </c>
       <c r="N6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="O6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
       </c>
       <c r="C7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G7" s="42" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="J7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M7" s="42" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="N7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1454,22 +1454,22 @@
       </c>
       <c r="C8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G8" s="42" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="J8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M8" s="42" t="inlineStr">
@@ -1509,22 +1509,22 @@
       </c>
       <c r="N8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G9" s="42" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="J9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" s="42" t="inlineStr">
@@ -1596,22 +1596,22 @@
       </c>
       <c r="N9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1628,22 +1628,22 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J10" s="42" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="K10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M10" s="42" t="inlineStr">
@@ -1683,22 +1683,22 @@
       </c>
       <c r="N10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1715,22 +1715,22 @@
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" s="42" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="L11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M11" s="42" t="inlineStr">
@@ -1770,22 +1770,22 @@
       </c>
       <c r="N11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1802,22 +1802,22 @@
       </c>
       <c r="C12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G12" s="42" t="inlineStr">
@@ -1857,22 +1857,22 @@
       </c>
       <c r="N12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1889,22 +1889,22 @@
       </c>
       <c r="C13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G13" s="42" t="inlineStr">
@@ -1944,22 +1944,22 @@
       </c>
       <c r="N13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1995,22 +1995,22 @@
       </c>
       <c r="C15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" s="42" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="H15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J15" s="42" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="K15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L15" s="42" t="inlineStr">
@@ -2050,22 +2050,22 @@
       </c>
       <c r="N15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2082,22 +2082,22 @@
       </c>
       <c r="C16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G16" s="42" t="inlineStr">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="K16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M16" s="42" t="inlineStr">
@@ -2137,22 +2137,22 @@
       </c>
       <c r="N16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2169,12 +2169,12 @@
       </c>
       <c r="C17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="E17" s="42" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G17" s="42" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="J17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K17" s="42" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="L17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M17" s="42" t="inlineStr">
@@ -2224,22 +2224,22 @@
       </c>
       <c r="N17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="O17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="F18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G18" s="42" t="inlineStr">
@@ -2311,22 +2311,22 @@
       </c>
       <c r="N18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D19" s="42" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="G19" s="42" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="I19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K19" s="42" t="inlineStr">
@@ -2403,17 +2403,17 @@
       </c>
       <c r="O19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D20" s="42" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L20" s="42" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="P20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1019,72 +1019,72 @@
       </c>
       <c r="C3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q3" s="42" t="inlineStr">
@@ -1106,52 +1106,52 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K4" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M4" s="42" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="O4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q4" s="42" t="inlineStr">
@@ -1193,77 +1193,77 @@
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1280,52 +1280,52 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="O6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="C7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F7" s="42" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="G7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -1407,17 +1407,17 @@
       </c>
       <c r="K7" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M7" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N7" s="42" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="O7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q7" s="42" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E8" s="42" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="H8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I8" s="42" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="K8" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L8" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M8" s="42" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="O8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q8" s="42" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="C9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E9" s="42" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I9" s="42" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K9" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" s="42" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="O9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q9" s="42" t="inlineStr">
@@ -1628,37 +1628,37 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J10" s="42" t="inlineStr">
@@ -1668,17 +1668,17 @@
       </c>
       <c r="K10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N10" s="42" t="inlineStr">
@@ -1688,17 +1688,17 @@
       </c>
       <c r="O10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E11" s="42" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I11" s="42" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="L11" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M11" s="42" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="O11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q11" s="42" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E12" s="42" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q12" s="42" t="inlineStr">
@@ -1894,12 +1894,12 @@
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F13" s="42" t="inlineStr">
@@ -1939,22 +1939,22 @@
       </c>
       <c r="M13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q13" s="42" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="C15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F15" s="42" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="I15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" s="42" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="K15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L15" s="42" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="M15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N15" s="42" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P15" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q15" s="42" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F16" s="42" t="inlineStr">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="K16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N16" s="42" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q16" s="42" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D17" s="42" t="inlineStr">
@@ -2184,17 +2184,17 @@
       </c>
       <c r="F17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" s="42" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="J17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K17" s="42" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="L17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M17" s="42" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Q17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="M18" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N18" s="42" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="O18" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P18" s="42" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H19" s="42" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="I19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K19" s="42" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Q19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" s="42" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L20" s="42" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N20" s="42" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Q20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="J3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K3" s="42" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M3" s="42" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Q3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1121,17 +1121,17 @@
       </c>
       <c r="F4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -1141,27 +1141,27 @@
       </c>
       <c r="J4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="K4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O4" s="42" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="P4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1203,22 +1203,22 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -1228,27 +1228,27 @@
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O5" s="42" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="P5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q5" s="42" t="inlineStr">
@@ -1290,27 +1290,27 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
@@ -1320,22 +1320,22 @@
       </c>
       <c r="K6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O6" s="42" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="P6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q6" s="42" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F7" s="42" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="G7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="K7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O7" s="42" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="P7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q7" s="42" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="H8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I8" s="42" t="inlineStr">
@@ -1494,22 +1494,22 @@
       </c>
       <c r="K8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O8" s="42" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="P8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q8" s="42" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I9" s="42" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="M9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O9" s="42" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="P9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q9" s="42" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I10" s="42" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O10" s="42" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q10" s="42" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="42" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I11" s="42" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="M11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N11" s="42" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="P11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q11" s="42" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" s="42" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="M12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N12" s="42" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="P12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q12" s="42" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="C13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" s="42" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N13" s="42" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="C15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E15" s="42" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="M15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N15" s="42" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P15" s="42" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="C16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E16" s="42" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="M16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N16" s="42" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P16" s="42" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D17" s="42" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G17" s="42" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="M17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N17" s="42" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="O17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P17" s="42" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="O18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P18" s="42" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D19" s="42" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G19" s="42" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="O19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P19" s="42" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D20" s="42" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="O20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P20" s="42" t="inlineStr">

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="J3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K3" s="42" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M3" s="42" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="P3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q3" s="42" t="inlineStr">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="F4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="J4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L4" s="42" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Q4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="K6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="C7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D7" s="42" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F7" s="42" t="inlineStr">
@@ -1387,17 +1387,17 @@
       </c>
       <c r="G7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J7" s="42" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="K7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L7" s="42" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="O7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="42" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="C8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F8" s="42" t="inlineStr">
@@ -1474,17 +1474,17 @@
       </c>
       <c r="G8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J8" s="42" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="K8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L8" s="42" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="O8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P8" s="42" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F9" s="42" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J9" s="42" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L9" s="42" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P9" s="42" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J10" s="42" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P10" s="42" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D11" s="42" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J11" s="42" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="K11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L11" s="42" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P11" s="42" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D12" s="42" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F12" s="42" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J12" s="42" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="K12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L12" s="42" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P12" s="42" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D13" s="42" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F13" s="42" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J13" s="42" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="K13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L13" s="42" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N13" s="42" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P13" s="42" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D15" s="42" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F15" s="42" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="I15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J15" s="42" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="K15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L15" s="42" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="M15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N15" s="42" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P15" s="42" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="C16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D16" s="42" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F16" s="42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="I16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J16" s="42" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="K16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L16" s="42" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="M16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N16" s="42" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P16" s="42" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D17" s="42" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F17" s="42" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="I17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J17" s="42" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="K17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L17" s="42" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="M17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N17" s="42" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="O17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P17" s="42" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="E18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F18" s="42" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="I18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J18" s="42" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="K18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L18" s="42" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="O18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P18" s="42" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D19" s="42" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F19" s="42" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J19" s="42" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="K19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L19" s="42" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="O19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P19" s="42" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="D20" s="42" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J20" s="42" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L20" s="42" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="O20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P20" s="42" t="inlineStr">

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F3" s="42" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="K3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L3" s="42" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="P3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q3" s="42" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F4" s="42" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="K4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M4" s="42" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="P4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="P5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="K6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1367,22 +1367,22 @@
       </c>
       <c r="C7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G7" s="42" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="H7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="K7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M7" s="42" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="O7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P7" s="42" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Q7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G8" s="42" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="H8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I8" s="42" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="K8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L8" s="42" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="O8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P8" s="42" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Q8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D9" s="42" t="inlineStr">
@@ -1551,22 +1551,22 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I9" s="42" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" s="42" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="M9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N9" s="42" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P9" s="42" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Q9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
@@ -1638,22 +1638,22 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I10" s="42" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N10" s="42" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P10" s="42" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Q10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D11" s="42" t="inlineStr">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H11" s="42" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="K11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L11" s="42" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="M11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P11" s="42" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Q11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D12" s="42" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H12" s="42" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="K12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L12" s="42" t="inlineStr">
@@ -1852,17 +1852,17 @@
       </c>
       <c r="M12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P12" s="42" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="Q12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D13" s="42" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F13" s="42" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="G13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H13" s="42" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="K13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L13" s="42" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="N13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P13" s="42" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="Q13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D15" s="42" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F15" s="42" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="G15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H15" s="42" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="K15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L15" s="42" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="N15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P15" s="42" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="C16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D16" s="42" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F16" s="42" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="G16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H16" s="42" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="K16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L16" s="42" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="N16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P16" s="42" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D17" s="42" t="inlineStr">
@@ -2179,17 +2179,17 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H17" s="42" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="K17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" s="42" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="N17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P17" s="42" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="E18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F18" s="42" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H18" s="42" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="K18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L18" s="42" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="N18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P18" s="42" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D19" s="42" t="inlineStr">
@@ -2353,17 +2353,17 @@
       </c>
       <c r="E19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H19" s="42" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="K19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L19" s="42" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="N19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P19" s="42" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="G20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H20" s="42" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="J20" s="42" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="L20" s="42" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="N20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P20" s="42" t="inlineStr">

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F3" s="42" t="inlineStr">
@@ -1116,62 +1116,62 @@
       </c>
       <c r="E4" s="42" t="inlineStr">
         <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="F4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="G4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="H4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="I4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="J4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="K4" s="42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="G4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="H4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="I4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="J4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="K4" s="42" t="inlineStr">
+      <c r="L4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="M4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="N4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="O4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="P4" s="42" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="L4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="M4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="N4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="O4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="P4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q4" s="42" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="M5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N5" s="42" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="P5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q5" s="42" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
@@ -1315,22 +1315,22 @@
       </c>
       <c r="J6" s="42" t="inlineStr">
         <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="K6" s="42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K6" s="42" t="inlineStr">
+      <c r="L6" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="M6" s="42" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="L6" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="M6" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E7" s="42" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" s="42" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="J7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K7" s="42" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="M7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N7" s="42" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Q7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E8" s="42" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="G8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" s="42" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="J8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K8" s="42" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="L8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N8" s="42" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Q8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="C9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E9" s="42" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="G9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" s="42" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K9" s="42" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="L9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M9" s="42" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Q9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E10" s="42" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" s="42" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K10" s="42" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Q10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E11" s="42" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" s="42" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="I11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K11" s="42" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Q11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E12" s="42" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="F12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" s="42" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="I12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K12" s="42" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="Q12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="C13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E13" s="42" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="G13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" s="42" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="I13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K13" s="42" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="Q13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1995,12 +1995,12 @@
       </c>
       <c r="C15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E15" s="42" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="G15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" s="42" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="I15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K15" s="42" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="C16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E16" s="42" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="G16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" s="42" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="I16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K16" s="42" t="inlineStr">
@@ -2169,57 +2169,57 @@
       </c>
       <c r="C17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N17" s="42" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="P17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" s="42" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="I18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K18" s="42" t="inlineStr">
@@ -2343,57 +2343,57 @@
       </c>
       <c r="C19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N19" s="42" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="P19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="G20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="H20" s="42" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="J20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K20" s="42" t="inlineStr">

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1019,77 +1019,77 @@
       </c>
       <c r="C3" s="42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="inlineStr">
+        <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="D3" s="42" t="inlineStr">
+      <c r="E3" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="E3" s="42" t="inlineStr">
+      <c r="H3" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="F3" s="42" t="inlineStr">
+      <c r="I3" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="G3" s="42" t="inlineStr">
+      <c r="J3" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="H3" s="42" t="inlineStr">
+      <c r="K3" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="I3" s="42" t="inlineStr">
+      <c r="M3" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="J3" s="42" t="inlineStr">
+      <c r="N3" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O3" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="K3" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L3" s="42" t="inlineStr">
+      <c r="P3" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="M3" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="N3" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="O3" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="P3" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
       <c r="Q3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1106,69 +1106,69 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F4" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="H4" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="K4" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L4" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M4" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="N4" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="H4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="I4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="J4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="K4" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="M4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="N4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="O4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
       <c r="P4" s="42" t="inlineStr">
         <is>
           <t>No</t>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Q4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1193,69 +1193,69 @@
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="42" t="inlineStr">
+        <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="H5" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="E5" s="42" t="inlineStr">
+      <c r="K5" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M5" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="F5" s="42" t="inlineStr">
+      <c r="N5" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="G5" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H5" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="J5" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="K5" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L5" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="M5" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N5" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="O5" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
       <c r="P5" s="42" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="Q5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1280,69 +1280,69 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E6" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
+      <c r="H6" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="E6" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F6" s="42" t="inlineStr">
+      <c r="K6" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O6" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="G6" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H6" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I6" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="J6" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="K6" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L6" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="M6" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N6" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="O6" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
       <c r="P6" s="42" t="inlineStr">
         <is>
           <t>No</t>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="C7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="42" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="F7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G7" s="42" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K7" s="42" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="L7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M7" s="42" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="N7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O7" s="42" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" s="42" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="F8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G8" s="42" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="I8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K8" s="42" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M8" s="42" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="N8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O8" s="42" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" s="42" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G9" s="42" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="I9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K9" s="42" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="L9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M9" s="42" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="N9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P9" s="42" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E10" s="42" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K10" s="42" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="N10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P10" s="42" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Q10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" s="42" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="J11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K11" s="42" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="N11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P11" s="42" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E12" s="42" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="J12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K12" s="42" t="inlineStr">
@@ -1857,12 +1857,12 @@
       </c>
       <c r="N12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P12" s="42" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" s="42" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K13" s="42" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="N13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P13" s="42" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E15" s="42" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="J15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K15" s="42" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="N15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O15" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P15" s="42" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E16" s="42" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="J16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K16" s="42" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="N16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O16" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P16" s="42" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="D17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E17" s="42" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="J17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K17" s="42" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="N17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O17" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P17" s="42" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="J18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K18" s="42" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="N18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O18" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P18" s="42" t="inlineStr">
@@ -2343,77 +2343,77 @@
       </c>
       <c r="C19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="K19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="O19" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="J20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="K20" s="42" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="N20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="O20" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P20" s="42" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Q20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D3" s="42" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F3" s="42" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="K3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L3" s="42" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="N3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P3" s="42" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Q3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D4" s="42" t="inlineStr">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="E4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G4" s="42" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="H4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J4" s="42" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M4" s="42" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="O4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q4" s="42" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J5" s="42" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="O5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P5" s="42" t="inlineStr">
@@ -1280,22 +1280,22 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="P6" s="42" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F7" s="42" t="inlineStr">
@@ -1387,17 +1387,17 @@
       </c>
       <c r="G7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J7" s="42" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="O7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="42" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F8" s="42" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="H8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J8" s="42" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="O8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P8" s="42" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F9" s="42" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J9" s="42" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I10" s="42" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Q10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I11" s="42" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I12" s="42" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="N13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O13" s="42" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="N17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O17" s="42" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G19" s="42" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Q20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1039,42 +1039,42 @@
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O3" s="42" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="P3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q3" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="F4" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="J4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="K4" s="42" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="L4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="N4" s="42" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="P4" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q4" s="42" t="inlineStr">
@@ -1198,14 +1198,14 @@
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" s="42" t="inlineStr">
+        <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="E5" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1213,22 +1213,22 @@
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N5" s="42" t="inlineStr">
@@ -1280,42 +1280,42 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E6" s="42" t="inlineStr">
+        <is>
           <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
-      <c r="E6" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
-        </is>
-      </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K6" s="42" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="P6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F7" s="42" t="inlineStr">
@@ -1387,17 +1387,17 @@
       </c>
       <c r="G7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J7" s="42" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="K7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L7" s="42" t="inlineStr">
@@ -1454,37 +1454,37 @@
       </c>
       <c r="C8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="F8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J8" s="42" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="K8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L8" s="42" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="O8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P8" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q8" s="42" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F9" s="42" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I9" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J9" s="42" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" s="42" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="M9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N9" s="42" t="inlineStr">
@@ -1638,27 +1638,27 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J10" s="42" t="inlineStr">
@@ -1668,17 +1668,17 @@
       </c>
       <c r="K10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N10" s="42" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="P10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I11" s="42" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" s="42" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="G13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H13" s="42" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N13" s="42" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="I16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J16" s="42" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="K16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L16" s="42" t="inlineStr">
@@ -2214,17 +2214,17 @@
       </c>
       <c r="L17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O17" s="42" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" s="42" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K19" s="42" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O19" s="42" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I20" s="42" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L20" s="42" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="M20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O20" s="42" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Q20" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/ourmodels_pincode.xlsx
+++ b/ourmodels_pincode.xlsx
@@ -1034,62 +1034,62 @@
       </c>
       <c r="F3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G3" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="P3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q3" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1121,62 +1121,62 @@
       </c>
       <c r="F4" s="42" t="inlineStr">
         <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="G4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="H4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="I4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="J4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="K4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="L4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="M4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="N4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="O4" s="42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H4" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I4" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K4" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L4" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M4" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N4" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O4" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="P4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q4" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E5" s="42" t="inlineStr">
@@ -1208,47 +1208,47 @@
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O5" s="42" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="P5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q5" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
@@ -1295,57 +1295,57 @@
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O6" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P6" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q6" s="42" t="inlineStr">
@@ -1367,62 +1367,62 @@
       </c>
       <c r="C7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="H7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K7" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O7" s="42" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="P7" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q7" s="42" t="inlineStr">
@@ -1454,77 +1454,77 @@
       </c>
       <c r="C8" s="42" t="inlineStr">
         <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="E8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="F8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="H8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="I8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="J8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="K8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="L8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="M8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="N8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="O8" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E8" s="42" t="inlineStr">
+      <c r="P8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="Q8" s="42" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="F8" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G8" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I8" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K8" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L8" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M8" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N8" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O8" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P8" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q8" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G9" s="42" t="inlineStr">
@@ -1566,37 +1566,37 @@
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K9" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="L9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M9" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O9" s="42" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="P9" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q9" s="42" t="inlineStr">
@@ -1628,62 +1628,62 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N10" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="O10" s="42" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="P10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q10" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1715,22 +1715,22 @@
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="G11" s="42" t="inlineStr">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="H11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="J11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K11" s="42" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="L11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N11" s="42" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="P11" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q11" s="42" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E12" s="42" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I12" s="42" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="J12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="K12" s="42" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="L12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N12" s="42" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="P12" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q12" s="42" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E13" s="42" t="inlineStr">
@@ -1904,17 +1904,17 @@
       </c>
       <c r="F13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I13" s="42" t="inlineStr">
@@ -1934,17 +1934,17 @@
       </c>
       <c r="L13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N13" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O13" s="42" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="P13" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q13" s="42" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E15" s="42" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="H15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I15" s="42" t="inlineStr">
@@ -2040,12 +2040,12 @@
       </c>
       <c r="L15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N15" s="42" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P15" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q15" s="42" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E16" s="42" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J16" s="42" t="inlineStr">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="K16" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N16" s="42" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="P16" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q16" s="42" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="D17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E17" s="42" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="H17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I17" s="42" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M17" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N17" s="42" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="P17" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q17" s="42" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="D18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="E18" s="42" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="H18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="I18" s="42" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="L18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="M18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N18" s="42" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="P18" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q18" s="42" t="inlineStr">
@@ -2358,57 +2358,57 @@
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" s="42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G19" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="H19" s="42" t="inlineStr">
         <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="I19" s="42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I19" s="42" t="inlineStr">
+      <c r="J19" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J19" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K19" s="42" t="inlineStr">
+      <c r="L19" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="M19" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="N19" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L19" s="42" t="inlineStr">
+      <c r="O19" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M19" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N19" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O19" s="42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="P19" s="42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="Q19" s="42" t="inlineStr">
@@ -2445,34 +2445,34 @@
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" s="42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G20" s="42" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
+        </is>
+      </c>
+      <c r="I20" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H20" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I20" s="42" t="inlineStr">
+      <c r="J20" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J20" s="42" t="inlineStr">
+      <c r="K20" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K20" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="L20" s="42" t="inlineStr">
         <is>
           <t>No</t>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="M20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">unknown: Click the button below to continue shopping Continue shopping Conditions of Use </t>
         </is>
       </c>
       <c r="N20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O20" s="42" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Q20" s="42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
